--- a/tdf_tippspiel_master.xlsx
+++ b/tdf_tippspiel_master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Auswertung Gesamt" sheetId="1" state="visible" r:id="rId3"/>
@@ -4142,7 +4142,8 @@
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="4" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="4" width="36.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="46.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="4" width="36.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="31.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="4" width="30.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="4" width="36.29"/>
